--- a/analyst/Franzi/rmonize/data_proc_elem/DPE_CARLA_FRANZI.xlsx
+++ b/analyst/Franzi/rmonize/data_proc_elem/DPE_CARLA_FRANZI.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Franzi\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9543C144-EB80-4814-8B6C-931848C1809E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8126E3FC-EB76-463D-9F0C-1DA87AEF73B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="263">
   <si>
     <t>index</t>
   </si>
@@ -901,9 +906,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -941,9 +946,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -976,26 +981,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1028,26 +1016,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2277,20 +2248,23 @@
       <c r="D40" t="s">
         <v>13</v>
       </c>
-      <c r="F40" t="s">
-        <v>88</v>
-      </c>
-      <c r="G40" t="s">
-        <v>260</v>
-      </c>
-      <c r="H40" t="s">
-        <v>260</v>
-      </c>
-      <c r="J40" t="s">
-        <v>258</v>
-      </c>
-      <c r="K40" t="s">
-        <v>259</v>
+      <c r="F40" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
@@ -2459,20 +2433,23 @@
       <c r="D47" t="s">
         <v>13</v>
       </c>
-      <c r="F47" t="s">
-        <v>102</v>
-      </c>
-      <c r="G47" t="s">
-        <v>260</v>
-      </c>
-      <c r="H47" t="s">
-        <v>260</v>
-      </c>
-      <c r="J47" t="s">
-        <v>258</v>
-      </c>
-      <c r="K47" t="s">
-        <v>259</v>
+      <c r="F47" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
@@ -2708,20 +2685,23 @@
       <c r="D56" t="s">
         <v>13</v>
       </c>
-      <c r="F56" t="s">
-        <v>120</v>
-      </c>
-      <c r="G56" t="s">
-        <v>260</v>
-      </c>
-      <c r="H56" t="s">
-        <v>260</v>
-      </c>
-      <c r="J56" t="s">
-        <v>258</v>
-      </c>
-      <c r="K56" t="s">
-        <v>259</v>
+      <c r="F56" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
@@ -3662,20 +3642,23 @@
       <c r="D92" t="s">
         <v>13</v>
       </c>
-      <c r="F92" t="s">
-        <v>192</v>
-      </c>
-      <c r="G92" t="s">
-        <v>260</v>
-      </c>
-      <c r="H92" t="s">
-        <v>260</v>
-      </c>
-      <c r="J92" t="s">
-        <v>258</v>
-      </c>
-      <c r="K92" t="s">
-        <v>259</v>
+      <c r="F92" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
@@ -4139,20 +4122,23 @@
       <c r="D110" t="s">
         <v>13</v>
       </c>
-      <c r="F110" t="s">
-        <v>228</v>
-      </c>
-      <c r="G110" t="s">
-        <v>260</v>
-      </c>
-      <c r="H110" t="s">
-        <v>260</v>
-      </c>
-      <c r="J110" t="s">
-        <v>258</v>
-      </c>
-      <c r="K110" t="s">
-        <v>259</v>
+      <c r="F110" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
